--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1000,25 +1000,7 @@
     <t>1422: source value from EM - DATE/TIME SPECIMEN TAKEN (#63.02-.01)</t>
   </si>
   <si>
-    <t>Pathology.ElectronMicroscopy.SpecimenTakenDateTime
-Pathology.EMComment.SpecimenTakenDateTime
-Pathology.EMDelayedComment.SpecimenTakenDateTime
-Pathology.EMDiagnosis.SpecimenTakenDateTime
-Pathology.EMGrossDescription.SpecimenTakenDateTime
-Pathology.EMMicroscopicExam.SpecimenTakenDateTime
-Pathology.EMOperativeFinding.SpecimenTakenDateTime
-Pathology.EMOrderedTest.SpecimenTakenDateTime
-Pathology.EMOrganTissueDisease.SpecimenTakenDateTime
-Pathology.EMOrganTissueFunction.SpecimenTakenDateTime
-Pathology.EMOrganTissueProcedure.SpecimenTakenDateTime
-Pathology.EMPostOpDiagnosis.SpecimenTakenDateTime
-Pathology.EMPreOpDiagnosis.SpecimenTakenDateTime
-Pathology.EMSpecimen.SpecimenTakenDateTime
-Pathology.EMSpecimenEPON.SpecimenTakenDateTime
-Pathology.EMSpecimenEPONProcedure.SpecimenTakenDateTime
-Pathology.EMSupplement.SpecimenTakenDateTime
-Pathology.EMSupplementDescript.SpecimenTakenDateTime
-Pathology.EMTIUReference.SpecimenTakenDateTime</t>
+    <t>Pathology.ElectronMicroscopy.SpecimenTakenDateTime,Pathology.EMComment.SpecimenTakenDateTime,Pathology.EMDelayedComment.SpecimenTakenDateTime,Pathology.EMDiagnosis.SpecimenTakenDateTime,Pathology.EMGrossDescription.SpecimenTakenDateTime,Pathology.EMMicroscopicExam.SpecimenTakenDateTime,Pathology.EMOperativeFinding.SpecimenTakenDateTime,Pathology.EMOrderedTest.SpecimenTakenDateTime,Pathology.EMOrganTissueDisease.SpecimenTakenDateTime,Pathology.EMOrganTissueFunction.SpecimenTakenDateTime,Pathology.EMOrganTissueProcedure.SpecimenTakenDateTime,Pathology.EMPostOpDiagnosis.SpecimenTakenDateTime,Pathology.EMPreOpDiagnosis.SpecimenTakenDateTime,Pathology.EMSpecimen.SpecimenTakenDateTime,Pathology.EMSpecimenEPON.SpecimenTakenDateTime,Pathology.EMSpecimenEPONProcedure.SpecimenTakenDateTime,Pathology.EMSupplement.SpecimenTakenDateTime,Pathology.EMSupplementDescript.SpecimenTakenDateTime,Pathology.EMTIUReference.SpecimenTakenDateTime</t>
   </si>
   <si>
     <t>DiagnosticReport.issued</t>
@@ -1915,7 +1897,7 @@
     <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="161.8203125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="61.08203125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Report
@@ -660,13 +660,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1604: source value from EM - ORDERED TEST &gt; ORDERED TEST - IEN (#63.02-.35 &gt; 63.52-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>1604: source value from EM - ORDERED TEST &gt; ORDERED TEST - IEN (#63.02-.35 &gt; 63.52-.001)</t>
   </si>
   <si>
     <t>DiagnosticReport.identifier.period</t>
@@ -739,6 +739,12 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
+    <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.02-.35 &gt; 63.52-3)</t>
+  </si>
+  <si>
+    <t>Pathology.EMOrderedTest.CPRSOrderIEN</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -746,12 +752,6 @@
   </si>
   <si>
     <t>outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.02-.35 &gt; 63.52-3)</t>
-  </si>
-  <si>
-    <t>Pathology.EMOrderedTest.CPRSOrderIEN</t>
   </si>
   <si>
     <t>DiagnosticReport.status</t>
@@ -773,6 +773,12 @@
 us-core-9</t>
   </si>
   <si>
+    <t>1414: terminologyMaps using VF_DiagnosticReportLabStatus on EM - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.02-.35 &gt; 63.52-10)</t>
+  </si>
+  <si>
+    <t>Pathology.EMOrderedTest.DispositionLabCodeIEN</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -783,12 +789,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1414: terminologyMaps using VF_DiagnosticReportLabStatus on EM - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.02-.35 &gt; 63.52-10)</t>
-  </si>
-  <si>
-    <t>Pathology.EMOrderedTest.DispositionLabCodeIEN</t>
   </si>
   <si>
     <t>DiagnosticReport.category</t>
@@ -1030,6 +1030,12 @@
 </t>
   </si>
   <si>
+    <t>1427: source value from EM - DATE REPORT COMPLETED (#63.02-.03)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.ReportCompleteDateTime</t>
+  </si>
+  <si>
     <t>OBR-22</t>
   </si>
   <si>
@@ -1037,12 +1043,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>1427: source value from EM - DATE REPORT COMPLETED (#63.02-.03)</t>
-  </si>
-  <si>
-    <t>Pathology.ElectronMicroscopy.ReportCompleteDateTime</t>
   </si>
   <si>
     <t>DiagnosticReport.performer</t>
@@ -1068,6 +1068,12 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
+    <t>1685: reference from ELECTRON MICROSCOPY - RELEASING SITE (#63.02-.345)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1078,12 +1084,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1685: reference from ELECTRON MICROSCOPY - RELEASING SITE (#63.02-.345)</t>
-  </si>
-  <si>
-    <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -1106,13 +1106,13 @@
     <t>Might not be the same entity that takes responsibility for the clinical report.</t>
   </si>
   <si>
+    <t>1696: reference from EM - PATHOLOGIST (#63.02-.02)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.PathologistStaffIEN</t>
+  </si>
+  <si>
     <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
-  </si>
-  <si>
-    <t>1696: reference from EM - PATHOLOGIST (#63.02-.02)</t>
-  </si>
-  <si>
-    <t>Pathology.ElectronMicroscopy.PathologistStaffIEN</t>
   </si>
   <si>
     <t>DiagnosticReport.specimen</t>
@@ -1134,13 +1134,13 @@
     <t>Need to be able to report information about the collected specimens on which the report is based.</t>
   </si>
   <si>
+    <t>1697: reference from EM - EM ACC # (#63.02-.06)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.ElectronMicroscopyAccession</t>
+  </si>
+  <si>
     <t>SPM</t>
-  </si>
-  <si>
-    <t>1697: reference from EM - EM ACC # (#63.02-.06)</t>
-  </si>
-  <si>
-    <t>Pathology.ElectronMicroscopy.ElectronMicroscopyAccession</t>
   </si>
   <si>
     <t>DiagnosticReport.result</t>
@@ -1268,10 +1268,10 @@
     <t>Reference to the image source.</t>
   </si>
   <si>
+    <t>1438: reference from EM - IMAGE (#63.02-2005)</t>
+  </si>
+  <si>
     <t>.value.reference</t>
-  </si>
-  <si>
-    <t>1438: reference from EM - IMAGE (#63.02-2005)</t>
   </si>
   <si>
     <t>DiagnosticReport.conclusion</t>
@@ -1290,13 +1290,13 @@
     <t>Need to be able to provide a conclusion that is not lost among the basic result data.</t>
   </si>
   <si>
+    <t>1441: source value from EM - EM DIAGNOSIS (#63.02-1.4)</t>
+  </si>
+  <si>
     <t>OBX</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode="SPRT"].source[classCode=OBS, moodCode=EVN, code=LOINC:48767-8].value (type=ST)</t>
-  </si>
-  <si>
-    <t>1441: source value from EM - EM DIAGNOSIS (#63.02-1.4)</t>
   </si>
   <si>
     <t>DiagnosticReport.conclusionCode</t>
@@ -1418,13 +1418,13 @@
     <t>Attachment.data</t>
   </si>
   <si>
+    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; REPORT TEXT (#63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
+  </si>
+  <si>
     <t>ED.5</t>
   </si>
   <si>
     <t>./data</t>
-  </si>
-  <si>
-    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; REPORT TEXT (#63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.url</t>
@@ -1892,12 +1892,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="161.8203125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="161.8203125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2130,19 +2130,19 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2734,13 +2734,13 @@
         <v>82</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>82</v>
@@ -2854,13 +2854,13 @@
         <v>82</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>82</v>
@@ -2974,13 +2974,13 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>82</v>
@@ -3096,13 +3096,13 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>82</v>
@@ -3212,22 +3212,22 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3336,13 +3336,13 @@
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3456,13 +3456,13 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>82</v>
@@ -3575,16 +3575,16 @@
         <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3697,16 +3697,16 @@
         <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3819,16 +3819,16 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -3936,16 +3936,16 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>209</v>
@@ -4057,16 +4057,16 @@
         <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4177,16 +4177,16 @@
         <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4305,13 +4305,13 @@
         <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4535,19 +4535,19 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4657,19 +4657,19 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4774,22 +4774,22 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4894,22 +4894,22 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5016,22 +5016,22 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5136,22 +5136,22 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5260,22 +5260,22 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5382,13 +5382,13 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>324</v>
@@ -5626,22 +5626,22 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>336</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5748,22 +5748,22 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="AP32" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5873,16 +5873,16 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5996,13 +5996,13 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6113,16 +6113,16 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6234,13 +6234,13 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6354,13 +6354,13 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6476,13 +6476,13 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6598,13 +6598,13 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6710,13 +6710,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6830,16 +6830,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>406</v>
@@ -6951,16 +6951,16 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7073,16 +7073,16 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7194,13 +7194,13 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7314,13 +7314,13 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7431,16 +7431,16 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7554,13 +7554,13 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7670,16 +7670,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>448</v>
@@ -7795,16 +7795,16 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7920,13 +7920,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8042,13 +8042,13 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8162,13 +8162,13 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8282,13 +8282,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="510">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -805,34 +805,6 @@
   </si>
   <si>
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:LaboratorySlice</t>
-  </si>
-  <si>
-    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -843,6 +815,98 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:LaboratorySlice</t>
+  </si>
+  <si>
+    <t>LaboratorySlice</t>
+  </si>
+  <si>
     <t>DiagnosticReport.code</t>
   </si>
   <si>
@@ -897,6 +961,12 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1150,7 +1220,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LaboratoryResultsObservation)
 </t>
   </si>
   <si>
@@ -1164,6 +1234,9 @@
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t>1437: reference from See mapping for Laboratory Results</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -1854,7 +1927,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP53"/>
+  <dimension ref="A1:AP57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -1892,7 +1965,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="161.8203125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="165.01953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
@@ -4480,7 +4553,7 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>82</v>
@@ -4495,19 +4568,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4532,7 +4605,7 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
@@ -4541,56 +4614,52 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4600,7 +4669,7 @@
         <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>82</v>
@@ -4615,13 +4684,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4639,19 +4708,19 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4663,13 +4732,13 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4681,35 +4750,35 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>267</v>
+        <v>166</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4735,43 +4804,43 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>264</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -4780,38 +4849,38 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>273</v>
+        <v>164</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -4820,17 +4889,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4879,13 +4950,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -4900,28 +4971,28 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4931,7 +5002,7 @@
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
@@ -4940,19 +5011,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>287</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5001,7 +5072,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5016,38 +5087,40 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5062,20 +5135,18 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>298</v>
+        <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>300</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5084,7 +5155,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5099,38 +5170,40 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
@@ -5142,34 +5215,32 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5184,20 +5255,18 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>311</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5221,13 +5290,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5245,53 +5314,53 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5306,19 +5375,17 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5367,7 +5434,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5376,50 +5443,50 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>326</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5428,19 +5495,19 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5489,13 +5556,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5504,41 +5571,41 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>92</v>
@@ -5550,19 +5617,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5599,68 +5666,68 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>92</v>
@@ -5669,22 +5736,22 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5733,56 +5800,56 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>92</v>
@@ -5791,22 +5858,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5855,49 +5922,49 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5907,27 +5974,29 @@
         <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5975,7 +6044,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5990,34 +6059,34 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6027,7 +6096,7 @@
         <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6036,17 +6105,19 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6095,7 +6166,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6110,30 +6181,30 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6144,10 +6215,10 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6156,16 +6227,20 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>161</v>
+        <v>374</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6213,34 +6288,34 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>163</v>
+        <v>372</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>164</v>
+        <v>306</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6255,7 +6330,7 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6265,7 +6340,7 @@
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6274,18 +6349,20 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>166</v>
+        <v>385</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6333,7 +6410,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>170</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6345,10 +6422,10 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
@@ -6357,10 +6434,10 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>164</v>
+        <v>390</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6368,14 +6445,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6388,26 +6465,24 @@
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>392</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6455,7 +6530,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6467,7 +6542,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6482,7 +6557,7 @@
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>134</v>
+        <v>396</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6490,21 +6565,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6513,22 +6588,20 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>160</v>
+        <v>399</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6577,13 +6650,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6601,10 +6674,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6612,10 +6685,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6623,28 +6696,28 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>394</v>
+        <v>160</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>395</v>
+        <v>161</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>396</v>
+        <v>162</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6695,10 +6768,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>163</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -6707,10 +6780,10 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
@@ -6722,7 +6795,7 @@
         <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>398</v>
+        <v>164</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6730,24 +6803,24 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>400</v>
+        <v>136</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -6756,18 +6829,18 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>401</v>
+        <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6815,22 +6888,22 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>399</v>
+        <v>170</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -6839,10 +6912,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>406</v>
+        <v>164</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6850,14 +6923,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6870,13 +6943,13 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>408</v>
@@ -6884,8 +6957,12 @@
       <c r="M42" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="N42" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6909,31 +6986,31 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6945,7 +7022,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -6957,10 +7034,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>412</v>
+        <v>134</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -6968,10 +7045,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6982,7 +7059,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6994,19 +7071,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7055,13 +7132,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7079,10 +7156,10 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7090,10 +7167,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7101,28 +7178,28 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>160</v>
+        <v>418</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>161</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>162</v>
+        <v>420</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7173,10 +7250,10 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>417</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>91</v>
@@ -7185,10 +7262,10 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7200,7 +7277,7 @@
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7208,24 +7285,24 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>136</v>
+        <v>424</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7234,18 +7311,18 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>138</v>
+        <v>425</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7281,34 +7358,34 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>170</v>
+        <v>423</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -7317,10 +7394,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>164</v>
+        <v>430</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7328,10 +7405,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7342,7 +7419,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7351,21 +7428,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>425</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7377,7 +7452,7 @@
         <v>82</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>82</v>
@@ -7389,13 +7464,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>176</v>
+        <v>255</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7413,13 +7488,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7437,10 +7512,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7448,10 +7523,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7462,7 +7537,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7471,20 +7546,22 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>111</v>
+        <v>438</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7497,7 +7574,7 @@
         <v>82</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>82</v>
@@ -7509,13 +7586,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7539,7 +7616,7 @@
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7557,10 +7634,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7568,10 +7645,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7585,7 +7662,7 @@
         <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -7594,20 +7671,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>441</v>
+        <v>161</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7655,7 +7728,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7667,10 +7740,10 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -7679,10 +7752,10 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>448</v>
+        <v>164</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7690,21 +7763,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7713,23 +7786,21 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>450</v>
+        <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>451</v>
+        <v>138</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>452</v>
+        <v>166</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7741,7 +7812,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -7765,31 +7836,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>456</v>
+        <v>170</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7801,10 +7872,10 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>458</v>
+        <v>164</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7812,10 +7883,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7838,19 +7909,17 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>460</v>
+        <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7863,7 +7932,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -7875,13 +7944,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7899,7 +7968,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7923,10 +7992,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7934,10 +8003,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7960,19 +8029,17 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>440</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7985,7 +8052,7 @@
         <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>82</v>
@@ -7997,13 +8064,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8021,7 +8088,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8048,7 +8115,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8056,10 +8123,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8073,26 +8140,28 @@
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>160</v>
+        <v>464</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8105,7 +8174,7 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>82</v>
@@ -8141,7 +8210,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8156,7 +8225,7 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
@@ -8165,10 +8234,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8176,10 +8245,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8202,17 +8271,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>311</v>
+        <v>474</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8225,7 +8296,7 @@
         <v>82</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>82</v>
@@ -8261,7 +8332,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8285,17 +8356,501 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="AP53" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP53">
+  <autoFilter ref="A1:AP57">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8305,7 +8860,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI56">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file EM (#63.02) to us-core-diagnosticreport-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file EM (63.02) to us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -660,7 +660,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1604: source value from EM - ORDERED TEST &gt; ORDERED TEST - IEN (#63.02-.35 &gt; 63.52-.001)</t>
+    <t>1604: source value from EM - ORDERED TEST &gt; ORDERED TEST - IEN (63.02-.35 &gt; 63.52-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -739,7 +739,7 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.02-.35 &gt; 63.52-3)</t>
+    <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.02-.35 &gt; 63.52-3)</t>
   </si>
   <si>
     <t>Pathology.EMOrderedTest.CPRSOrderIEN</t>
@@ -773,7 +773,7 @@
 us-core-9</t>
   </si>
   <si>
-    <t>1414: terminologyMaps using VF_DiagnosticReportLabStatus on EM - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.02-.35 &gt; 63.52-10)</t>
+    <t>1414: terminologyMaps using VF_DiagnosticReportLabStatus on EM - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (63.02-.35 &gt; 63.52-10)</t>
   </si>
   <si>
     <t>Pathology.EMOrderedTest.DispositionLabCodeIEN</t>
@@ -892,7 +892,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -961,7 +961,7 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1067,7 +1067,7 @@
 </t>
   </si>
   <si>
-    <t>1422: source value from EM - DATE/TIME SPECIMEN TAKEN (#63.02-.01)</t>
+    <t>1422: source value from EM - DATE/TIME SPECIMEN TAKEN (63.02-.01)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.SpecimenTakenDateTime,Pathology.EMComment.SpecimenTakenDateTime,Pathology.EMDelayedComment.SpecimenTakenDateTime,Pathology.EMDiagnosis.SpecimenTakenDateTime,Pathology.EMGrossDescription.SpecimenTakenDateTime,Pathology.EMMicroscopicExam.SpecimenTakenDateTime,Pathology.EMOperativeFinding.SpecimenTakenDateTime,Pathology.EMOrderedTest.SpecimenTakenDateTime,Pathology.EMOrganTissueDisease.SpecimenTakenDateTime,Pathology.EMOrganTissueFunction.SpecimenTakenDateTime,Pathology.EMOrganTissueProcedure.SpecimenTakenDateTime,Pathology.EMPostOpDiagnosis.SpecimenTakenDateTime,Pathology.EMPreOpDiagnosis.SpecimenTakenDateTime,Pathology.EMSpecimen.SpecimenTakenDateTime,Pathology.EMSpecimenEPON.SpecimenTakenDateTime,Pathology.EMSpecimenEPONProcedure.SpecimenTakenDateTime,Pathology.EMSupplement.SpecimenTakenDateTime,Pathology.EMSupplementDescript.SpecimenTakenDateTime,Pathology.EMTIUReference.SpecimenTakenDateTime</t>
@@ -1100,7 +1100,7 @@
 </t>
   </si>
   <si>
-    <t>1427: source value from EM - DATE REPORT COMPLETED (#63.02-.03)</t>
+    <t>1427: source value from EM - DATE REPORT COMPLETED (63.02-.03)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ReportCompleteDateTime</t>
@@ -1138,7 +1138,7 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
-    <t>1685: reference from ELECTRON MICROSCOPY - RELEASING SITE (#63.02-.345)</t>
+    <t>1685: reference from ELECTRON MICROSCOPY - RELEASING SITE (63.02-.345)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN</t>
@@ -1176,7 +1176,7 @@
     <t>Might not be the same entity that takes responsibility for the clinical report.</t>
   </si>
   <si>
-    <t>1696: reference from EM - PATHOLOGIST (#63.02-.02)</t>
+    <t>1696: reference from EM - PATHOLOGIST (63.02-.02)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.PathologistStaffIEN</t>
@@ -1204,7 +1204,7 @@
     <t>Need to be able to report information about the collected specimens on which the report is based.</t>
   </si>
   <si>
-    <t>1697: reference from EM - EM ACC # (#63.02-.06)</t>
+    <t>1697: reference from EM - EM ACC # (63.02-.06)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ElectronMicroscopyAccession</t>
@@ -1341,7 +1341,7 @@
     <t>Reference to the image source.</t>
   </si>
   <si>
-    <t>1438: reference from EM - IMAGE (#63.02-2005)</t>
+    <t>1438: reference from EM - IMAGE (63.02-2005)</t>
   </si>
   <si>
     <t>.value.reference</t>
@@ -1363,7 +1363,7 @@
     <t>Need to be able to provide a conclusion that is not lost among the basic result data.</t>
   </si>
   <si>
-    <t>1441: source value from EM - EM DIAGNOSIS (#63.02-1.4)</t>
+    <t>1441: source value from EM - EM DIAGNOSIS (63.02-1.4)</t>
   </si>
   <si>
     <t>OBX</t>
@@ -1491,7 +1491,7 @@
     <t>Attachment.data</t>
   </si>
   <si>
-    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; REPORT TEXT (#63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
+    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; REPORT TEXT (63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
   </si>
   <si>
     <t>ED.5</t>
@@ -1965,7 +1965,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="517">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -805,6 +805,95 @@
   </si>
   <si>
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:LaboratorySlice</t>
+  </si>
+  <si>
+    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -815,96 +904,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:LaboratorySlice</t>
-  </si>
-  <si>
-    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -939,6 +939,27 @@
   </si>
   <si>
     <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding</t>
+  </si>
+  <si>
+    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.text</t>
+  </si>
+  <si>
+    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.LabChemTestName</t>
   </si>
   <si>
     <t>DiagnosticReport.subject</t>
@@ -1927,7 +1948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP57"/>
+  <dimension ref="A1:AP61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -4553,34 +4574,34 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X22" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X22" t="s" s="2">
+      <c r="Y22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Y22" t="s" s="2">
+      <c r="Z22" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AA22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB22" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4605,30 +4626,30 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4743,10 +4764,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4863,10 +4884,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4889,19 +4910,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4950,7 +4971,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4974,10 +4995,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4985,10 +5006,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5014,16 +5035,16 @@
         <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5072,7 +5093,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5087,19 +5108,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5107,13 +5128,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>250</v>
@@ -5155,28 +5176,28 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X27" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="T27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X27" t="s" s="2">
+      <c r="Y27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5209,7 +5230,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5218,13 +5239,13 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5356,37 +5377,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>161</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
+        <v>162</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>301</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5434,7 +5453,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>163</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5446,44 +5465,44 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>306</v>
+        <v>164</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>309</v>
+        <v>136</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5492,23 +5511,21 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>310</v>
+        <v>137</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>138</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
+        <v>166</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5544,31 +5561,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5577,35 +5594,35 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>317</v>
+        <v>164</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>92</v>
@@ -5617,19 +5634,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>321</v>
+        <v>264</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>322</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>324</v>
+        <v>267</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>325</v>
+        <v>268</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5666,61 +5683,61 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>329</v>
+        <v>270</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>330</v>
+        <v>271</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5739,19 +5756,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>334</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5800,7 +5817,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5809,44 +5826,44 @@
         <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>91</v>
@@ -5861,19 +5878,17 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5922,7 +5937,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5931,50 +5946,50 @@
         <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>349</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -5983,19 +5998,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>354</v>
+        <v>319</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6044,13 +6059,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6059,41 +6074,41 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>362</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>92</v>
@@ -6105,19 +6120,19 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>365</v>
+        <v>328</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6154,68 +6169,68 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>371</v>
+        <v>336</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>362</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>92</v>
@@ -6224,22 +6239,22 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6288,56 +6303,56 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>382</v>
+        <v>345</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>92</v>
@@ -6346,22 +6361,22 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>383</v>
+        <v>346</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6410,49 +6425,49 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>390</v>
+        <v>355</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6462,27 +6477,29 @@
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>392</v>
+        <v>359</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>361</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6530,7 +6547,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6545,34 +6562,34 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6582,7 +6599,7 @@
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6591,17 +6608,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>402</v>
+        <v>363</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6650,7 +6669,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6665,30 +6684,30 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6699,10 +6718,10 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -6711,16 +6730,20 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>161</v>
+        <v>381</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6768,34 +6791,34 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>163</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6803,14 +6826,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>389</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6820,7 +6843,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -6829,18 +6852,20 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>390</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>391</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>166</v>
+        <v>392</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6888,7 +6913,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>170</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6900,10 +6925,10 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -6912,10 +6937,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>164</v>
+        <v>397</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6923,14 +6948,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6943,26 +6968,24 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>399</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7010,7 +7033,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7022,7 +7045,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7037,7 +7060,7 @@
         <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>134</v>
+        <v>403</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7045,21 +7068,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7068,22 +7091,20 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>160</v>
+        <v>406</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7132,13 +7153,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7156,10 +7177,10 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7167,10 +7188,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7178,28 +7199,28 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>418</v>
+        <v>160</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>161</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>162</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7250,10 +7271,10 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>163</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>91</v>
@@ -7262,10 +7283,10 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7277,7 +7298,7 @@
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7285,24 +7306,24 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>424</v>
+        <v>136</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7311,18 +7332,18 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>425</v>
+        <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7370,22 +7391,22 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>423</v>
+        <v>170</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -7394,10 +7415,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>430</v>
+        <v>164</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7405,14 +7426,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7425,22 +7446,26 @@
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7464,13 +7489,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7488,7 +7513,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7500,7 +7525,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7512,10 +7537,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>436</v>
+        <v>134</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7523,10 +7548,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7537,7 +7562,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7549,19 +7574,19 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>438</v>
+        <v>160</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7610,13 +7635,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7634,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7645,10 +7670,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7656,28 +7681,28 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>160</v>
+        <v>425</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>161</v>
+        <v>426</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7728,10 +7753,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>163</v>
+        <v>424</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>91</v>
@@ -7740,10 +7765,10 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -7755,7 +7780,7 @@
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>164</v>
+        <v>429</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7763,24 +7788,24 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
@@ -7789,18 +7814,18 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>138</v>
+        <v>432</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7836,34 +7861,34 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>170</v>
+        <v>430</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
@@ -7872,10 +7897,10 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>164</v>
+        <v>437</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7883,10 +7908,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7897,7 +7922,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7906,21 +7931,19 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>449</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7932,7 +7955,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -7944,13 +7967,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7968,13 +7991,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -7992,10 +8015,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8003,10 +8026,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8017,7 +8040,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8026,20 +8049,22 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>445</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8052,7 +8077,7 @@
         <v>82</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>82</v>
@@ -8064,13 +8089,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8088,13 +8113,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8112,10 +8137,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8123,10 +8148,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8140,7 +8165,7 @@
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8149,20 +8174,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>464</v>
+        <v>160</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>161</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8210,7 +8231,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>469</v>
+        <v>163</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8222,10 +8243,10 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
@@ -8234,10 +8255,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>472</v>
+        <v>164</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8245,21 +8266,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8268,23 +8289,21 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>474</v>
+        <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>475</v>
+        <v>138</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>476</v>
+        <v>166</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8296,7 +8315,7 @@
         <v>82</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>82</v>
@@ -8320,31 +8339,31 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>480</v>
+        <v>170</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8356,10 +8375,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>482</v>
+        <v>164</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8367,10 +8386,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8393,19 +8412,17 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>484</v>
+        <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8418,7 +8435,7 @@
         <v>82</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>82</v>
@@ -8430,13 +8447,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8454,7 +8471,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8478,10 +8495,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8489,10 +8506,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8515,19 +8532,17 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="M55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8540,7 +8555,7 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>82</v>
@@ -8552,13 +8567,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8576,7 +8591,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>496</v>
+        <v>468</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8603,7 +8618,7 @@
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>497</v>
+        <v>469</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8611,10 +8626,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8628,26 +8643,28 @@
         <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>160</v>
+        <v>471</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8660,7 +8677,7 @@
         <v>82</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>82</v>
@@ -8696,7 +8713,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8711,7 +8728,7 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
@@ -8720,10 +8737,10 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8731,10 +8748,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8757,17 +8774,19 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>334</v>
+        <v>481</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8780,7 +8799,7 @@
         <v>82</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>82</v>
@@ -8816,7 +8835,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8840,17 +8859,501 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AO57" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AP57" t="s" s="2">
+      <c r="B58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP57">
+  <autoFilter ref="A1:AP61">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8860,7 +9363,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -881,7 +881,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1159,7 +1159,7 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
-    <t>1685: reference from ELECTRON MICROSCOPY - RELEASING SITE (63.02-.345)</t>
+    <t>1685: reference from EM - RELEASING SITE (63.02-.345)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN</t>
@@ -1512,7 +1512,7 @@
     <t>Attachment.data</t>
   </si>
   <si>
-    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; REPORT TEXT (63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
+    <t>1720: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; TIU DOCUMENT - REPORT TEXT (63.02-.16 &gt; 63.49-1 &gt; 8925-2)</t>
   </si>
   <si>
     <t>ED.5</t>
@@ -1986,7 +1986,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="176.40234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$68</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="561">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -742,7 +742,7 @@
     <t>1689: reference from EM - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.02-.35 &gt; 63.52-3)</t>
   </si>
   <si>
-    <t>Pathology.EMOrderedTest.CPRSOrderIEN</t>
+    <t>Pathology.EMOrderedTest.CPRSOrderIEN,Pathology.EMOrderedTest.CPRSOrderSID</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -776,7 +776,7 @@
     <t>1414: terminologyMaps using VF_DiagnosticReportLabStatus on EM - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (63.02-.35 &gt; 63.52-10)</t>
   </si>
   <si>
-    <t>Pathology.EMOrderedTest.DispositionLabCodeIEN</t>
+    <t>Pathology.EMOrderedTest.DispositionLabCodeIEN,Pathology.EMOrderedTest.DispositionLabCodeSID</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -882,6 +882,9 @@
   </si>
   <si>
     <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -923,12 +926,24 @@
     <t>UsageNote= The typical patterns for codes are:  1)  a LOINC code either as a  translation from a "local" code or as a primary code, or 2)  a local code only if no suitable LOINC exists,  or 3)  both the local and the LOINC translation.   Systems SHALL be capable of sending the local code if one exists.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="50668-3"/&gt;
+    &lt;display value="Microscopic observation in Unspecified specimen by Electron microscopy Narrative"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>LOINC codes</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-lab-codes</t>
   </si>
   <si>
+    <t>1813: fixed value = http://loinc.org#50668-3 Microscopic observation in Unspecified specimen by Electron microscopy Narrative</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -951,6 +966,130 @@
   </si>
   <si>
     <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1814: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - CODING SYSTEM &gt; CODING SYSTEM - CODE &gt; CODE - CODE (63.02-.16 &gt; 63.49-1 &gt; 8925-.01 &gt; 8925.1-1501 &gt; 8926.1-2 &gt; 8926.12-.02 &gt; 8926.121-.01)</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>DiagnosticReport.code.text</t>
@@ -985,7 +1124,7 @@
     <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1091,7 +1230,7 @@
     <t>1422: source value from EM - DATE/TIME SPECIMEN TAKEN (63.02-.01)</t>
   </si>
   <si>
-    <t>Pathology.ElectronMicroscopy.SpecimenTakenDateTime,Pathology.EMComment.SpecimenTakenDateTime,Pathology.EMDelayedComment.SpecimenTakenDateTime,Pathology.EMDiagnosis.SpecimenTakenDateTime,Pathology.EMGrossDescription.SpecimenTakenDateTime,Pathology.EMMicroscopicExam.SpecimenTakenDateTime,Pathology.EMOperativeFinding.SpecimenTakenDateTime,Pathology.EMOrderedTest.SpecimenTakenDateTime,Pathology.EMOrganTissueDisease.SpecimenTakenDateTime,Pathology.EMOrganTissueFunction.SpecimenTakenDateTime,Pathology.EMOrganTissueProcedure.SpecimenTakenDateTime,Pathology.EMPostOpDiagnosis.SpecimenTakenDateTime,Pathology.EMPreOpDiagnosis.SpecimenTakenDateTime,Pathology.EMSpecimen.SpecimenTakenDateTime,Pathology.EMSpecimenEPON.SpecimenTakenDateTime,Pathology.EMSpecimenEPONProcedure.SpecimenTakenDateTime,Pathology.EMSupplement.SpecimenTakenDateTime,Pathology.EMSupplementDescript.SpecimenTakenDateTime,Pathology.EMTIUReference.SpecimenTakenDateTime</t>
+    <t>Pathology.ElectronMicroscopy.SpecimenTakenDateTime,Pathology.EMComment.SpecimenTakenDateTime,Pathology.EMDelayedComment.SpecimenTakenDateTime,Pathology.EMDiagnosis.SpecimenTakenDateTime,Pathology.EMGrossDescription.SpecimenTakenDateTime,Pathology.EMMicroscopicExam.SpecimenTakenDateTime,Pathology.EMOperativeFinding.SpecimenTakenDateTime,Pathology.EMOrderedTest.SpecimenTakenDateTime,Pathology.EMOrganTissueDisease.SpecimenTakenDateTime,Pathology.EMOrganTissueEtiology.SpecimenTakenDateTime,Pathology.EMOrganTissueFunction.SpecimenTakenDateTime,Pathology.EMOrganTissueMorphology.SpecimenTakenDateTime,Pathology.EMOrganTissueProcedure.SpecimenTakenDateTime,Pathology.EMPostOpDiagnosis.SpecimenTakenDateTime,Pathology.EMPreOpDiagnosis.SpecimenTakenDateTime,Pathology.EMSpecimen.SpecimenTakenDateTime,Pathology.EMSpecimenEPON.SpecimenTakenDateTime,Pathology.EMSpecimenEPONProcedure.SpecimenTakenDateTime,Pathology.EMSupplement.SpecimenTakenDateTime,Pathology.EMSupplementDescript.SpecimenTakenDateTime,Pathology.EMTIUReference.SpecimenTakenDateTime</t>
   </si>
   <si>
     <t>DiagnosticReport.issued</t>
@@ -1162,7 +1301,7 @@
     <t>1685: reference from EM - RELEASING SITE (63.02-.345)</t>
   </si>
   <si>
-    <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN</t>
+    <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN,Pathology.ElectronMicroscopy.ReleasingInstitutionSID</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1200,7 +1339,7 @@
     <t>1696: reference from EM - PATHOLOGIST (63.02-.02)</t>
   </si>
   <si>
-    <t>Pathology.ElectronMicroscopy.PathologistStaffIEN</t>
+    <t>Pathology.ElectronMicroscopy.PathologistStaffIEN,Pathology.ElectronMicroscopy.PathologistStaffSID</t>
   </si>
   <si>
     <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
@@ -1948,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AP68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -1986,7 +2125,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="176.40234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
@@ -5111,16 +5250,16 @@
         <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5128,13 +5267,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>250</v>
@@ -5176,7 +5315,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5230,7 +5369,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5250,14 +5389,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5279,13 +5418,13 @@
         <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5296,7 +5435,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5314,10 +5453,10 @@
         <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5335,7 +5474,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5350,30 +5489,30 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5488,10 +5627,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5608,10 +5747,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5710,10 +5849,10 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
@@ -5730,10 +5869,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5747,29 +5886,25 @@
         <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5817,7 +5952,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5829,22 +5964,22 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>280</v>
+        <v>164</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5852,44 +5987,44 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>304</v>
+        <v>136</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5925,61 +6060,61 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5998,19 +6133,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>317</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6059,7 +6194,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6080,28 +6215,28 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6111,7 +6246,7 @@
         <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6120,20 +6255,18 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>328</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6169,17 +6302,19 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6188,7 +6323,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
@@ -6200,30 +6335,28 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6242,19 +6375,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>341</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6303,7 +6434,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6312,40 +6443,40 @@
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6355,7 +6486,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6364,19 +6495,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>346</v>
+        <v>160</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6425,7 +6554,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6434,50 +6563,50 @@
         <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6486,19 +6615,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6547,13 +6676,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6562,41 +6691,41 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>92</v>
@@ -6608,19 +6737,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>372</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>374</v>
+        <v>274</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>363</v>
+        <v>276</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6669,13 +6798,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>370</v>
+        <v>277</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6684,41 +6813,41 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>378</v>
+        <v>280</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>368</v>
+        <v>281</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>92</v>
@@ -6727,22 +6856,20 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6791,13 +6918,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6806,65 +6933,65 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>386</v>
+        <v>354</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6913,13 +7040,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -6928,64 +7055,66 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>396</v>
+        <v>367</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7021,28 +7150,26 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
@@ -7054,38 +7181,40 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="D43" t="s" s="2">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
@@ -7094,17 +7223,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7153,49 +7284,49 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7205,25 +7336,29 @@
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>160</v>
+        <v>390</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>161</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7271,7 +7406,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7280,40 +7415,40 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>164</v>
+        <v>399</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>136</v>
+        <v>402</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7323,27 +7458,29 @@
         <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>403</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>138</v>
+        <v>404</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>166</v>
+        <v>405</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7391,7 +7528,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>170</v>
+        <v>401</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7403,37 +7540,37 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>164</v>
+        <v>412</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7443,28 +7580,28 @@
         <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>137</v>
+        <v>416</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>140</v>
+        <v>419</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>146</v>
+        <v>407</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7513,7 +7650,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7525,33 +7662,33 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>134</v>
+        <v>412</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7562,10 +7699,10 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -7574,19 +7711,19 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>424</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7635,13 +7772,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7650,19 +7787,19 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>423</v>
+        <v>357</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7670,21 +7807,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>92</v>
@@ -7693,19 +7830,23 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7753,13 +7894,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7768,7 +7909,7 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -7777,10 +7918,10 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7788,24 +7929,24 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
@@ -7814,18 +7955,18 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>160</v>
+        <v>443</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7873,13 +8014,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7888,7 +8029,7 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
@@ -7897,10 +8038,10 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7908,14 +8049,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7931,19 +8072,21 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>182</v>
+        <v>450</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7967,13 +8110,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7991,7 +8134,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8015,10 +8158,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8026,10 +8169,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8040,7 +8183,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8052,20 +8195,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>445</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>446</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8113,19 +8252,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>444</v>
+        <v>163</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8137,10 +8276,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>450</v>
+        <v>164</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8148,21 +8287,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8174,15 +8313,17 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8231,19 +8372,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8266,14 +8407,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>136</v>
+        <v>458</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8286,24 +8427,26 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>138</v>
+        <v>459</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>166</v>
+        <v>460</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8339,19 +8482,19 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>170</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8378,7 +8521,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8386,10 +8529,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8409,20 +8552,22 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8435,7 +8580,7 @@
         <v>82</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>82</v>
@@ -8447,13 +8592,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8471,7 +8616,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8495,10 +8640,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8506,10 +8651,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8517,13 +8662,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -8532,18 +8677,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>111</v>
+        <v>469</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>466</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8555,7 +8698,7 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>82</v>
@@ -8567,13 +8710,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8594,7 +8737,7 @@
         <v>468</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8606,7 +8749,7 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
@@ -8618,7 +8761,7 @@
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8626,14 +8769,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8652,19 +8795,17 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>471</v>
+        <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8713,7 +8854,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8728,7 +8869,7 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
@@ -8737,10 +8878,10 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8748,10 +8889,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8762,7 +8903,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8771,23 +8912,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>481</v>
+        <v>182</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N57" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="O57" t="s" s="2">
-        <v>485</v>
-      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8799,26 +8936,26 @@
         <v>82</v>
       </c>
       <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="U57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8835,13 +8972,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -8859,10 +8996,10 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8870,10 +9007,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8884,7 +9021,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -8893,22 +9030,22 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8957,13 +9094,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -8981,10 +9118,10 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8992,10 +9129,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9015,23 +9152,19 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>471</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>499</v>
+        <v>161</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9079,7 +9212,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>163</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9091,7 +9224,7 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9106,7 +9239,7 @@
         <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>504</v>
+        <v>164</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9114,21 +9247,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9137,21 +9270,21 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>506</v>
+        <v>138</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9163,7 +9296,7 @@
         <v>82</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>82</v>
@@ -9187,31 +9320,31 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>510</v>
+        <v>170</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9226,7 +9359,7 @@
         <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>511</v>
+        <v>164</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9234,10 +9367,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9260,17 +9393,17 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>341</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9283,7 +9416,7 @@
         <v>82</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>82</v>
@@ -9295,13 +9428,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9319,7 +9452,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9343,17 +9476,865 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP61">
+  <autoFilter ref="A1:AP68">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9363,7 +10344,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -930,7 +930,7 @@
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
     &lt;code value="50668-3"/&gt;
-    &lt;display value="Microscopic observation in Unspecified specimen by Electron microscopy Narrative"/&gt;
+    &lt;display value="Microscopic observation in Specimen by Electron microscopy Narrative"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -941,7 +941,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-lab-codes</t>
   </si>
   <si>
-    <t>1813: fixed value = http://loinc.org#50668-3 Microscopic observation in Unspecified specimen by Electron microscopy Narrative</t>
+    <t>1813: fixed value = http://loinc.org#50668-3 Microscopic observation in Specimen by Electron microscopy Narrative</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,10 +630,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1604-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -989,9 +995,15 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
+    <t>1420-2: fixed value = http://loinc.org</t>
+  </si>
+  <si>
     <t>C*E.3</t>
   </si>
   <si>
@@ -1034,7 +1046,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1814: source value from EM - TIU REFERENCE DATE/TIME - EM &gt; TIU REFERENCE DATE/TIME - EM - TIU ENTRY POINTER - EM &gt; TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - CODING SYSTEM &gt; CODING SYSTEM - CODE &gt; CODE - CODE (63.02-.16 &gt; 63.49-1 &gt; 8925-.01 &gt; 8925.1-1501 &gt; 8926.1-2 &gt; 8926.12-.02 &gt; 8926.121-.01)</t>
+    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1056,6 +1068,9 @@
   </si>
   <si>
     <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1298,22 +1313,48 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>PRT-8 (where this PRT-4-Participation = "PO")</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.performer:va-by</t>
+  </si>
+  <si>
+    <t>va-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+</t>
+  </si>
+  <si>
+    <t>1432: reference from EM - RELEASED BY (63.02-.13)</t>
+  </si>
+  <si>
+    <t>Pathology.ElectronMicroscopy.ReleasedByStaffIEN,Pathology.ElectronMicroscopy.ReleasedByStaffSID</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.performer:va-at</t>
+  </si>
+  <si>
+    <t>va-at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+</t>
+  </si>
+  <si>
     <t>1685: reference from EM - RELEASING SITE (63.02-.345)</t>
   </si>
   <si>
     <t>Pathology.ElectronMicroscopy.ReleasingInstitutionIEN,Pathology.ElectronMicroscopy.ReleasingInstitutionSID</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>PRT-8 (where this PRT-4-Participation = "PO")</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -2087,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP68"/>
+  <dimension ref="A1:AP70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -2125,7 +2166,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="176.40234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
@@ -3964,7 +4005,7 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -3995,10 +4036,10 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>82</v>
@@ -4034,7 +4075,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4049,7 +4090,7 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
@@ -4058,10 +4099,10 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -4069,10 +4110,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4098,13 +4139,13 @@
         <v>160</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4118,7 +4159,7 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4154,7 +4195,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4169,7 +4210,7 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4178,10 +4219,10 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4189,10 +4230,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4215,13 +4256,13 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4272,7 +4313,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4296,10 +4337,10 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4307,10 +4348,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4333,16 +4374,16 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4392,7 +4433,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4416,10 +4457,10 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4427,14 +4468,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4453,19 +4494,19 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4514,7 +4555,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4529,19 +4570,19 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4549,10 +4590,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4578,14 +4619,14 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4614,7 +4655,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4632,7 +4673,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4641,40 +4682,40 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4696,13 +4737,13 @@
         <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4728,19 +4769,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4750,7 +4791,7 @@
         <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4774,21 +4815,21 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4903,10 +4944,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5023,10 +5064,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5049,19 +5090,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5110,7 +5151,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5134,10 +5175,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5145,10 +5186,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5174,16 +5215,16 @@
         <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5232,7 +5273,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5247,19 +5288,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5267,16 +5308,16 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5298,13 +5339,13 @@
         <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5315,7 +5356,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5330,13 +5371,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5354,7 +5395,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5369,7 +5410,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5378,25 +5419,25 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5418,13 +5459,13 @@
         <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5435,7 +5476,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5453,10 +5494,10 @@
         <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5474,7 +5515,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5489,30 +5530,30 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5627,10 +5668,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5747,10 +5788,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5773,19 +5814,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5834,7 +5875,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5849,19 +5890,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5869,10 +5910,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5987,10 +6028,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6107,10 +6148,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6124,7 +6165,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6136,16 +6177,16 @@
         <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6155,7 +6196,7 @@
         <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>82</v>
@@ -6194,7 +6235,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6209,7 +6250,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
@@ -6218,10 +6259,10 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6229,10 +6270,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6258,13 +6299,13 @@
         <v>160</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6314,7 +6355,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6338,10 +6379,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6349,10 +6390,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6378,14 +6419,14 @@
         <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6434,7 +6475,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6449,19 +6490,19 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6469,10 +6510,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6486,7 +6527,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6498,14 +6539,14 @@
         <v>160</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6554,7 +6595,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6569,19 +6610,19 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6589,10 +6630,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6615,19 +6656,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6676,7 +6717,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6700,10 +6741,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6711,10 +6752,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6740,16 +6781,16 @@
         <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6798,7 +6839,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6813,19 +6854,19 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6833,14 +6874,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6859,17 +6900,17 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6918,7 +6959,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6933,34 +6974,34 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6979,19 +7020,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7040,7 +7081,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7061,28 +7102,28 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7101,19 +7142,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7150,7 +7191,7 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7160,7 +7201,7 @@
         <v>169</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7169,7 +7210,7 @@
         <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
@@ -7181,30 +7222,30 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7223,19 +7264,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7284,7 +7325,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7293,40 +7334,40 @@
         <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7345,19 +7386,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7406,7 +7447,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7415,40 +7456,40 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7467,19 +7508,19 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7516,19 +7557,17 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7543,41 +7582,43 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>92</v>
@@ -7589,19 +7630,19 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7650,7 +7691,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7671,35 +7712,37 @@
         <v>421</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="B47" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>92</v>
@@ -7708,22 +7751,22 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>424</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7772,7 +7815,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7787,34 +7830,34 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7830,22 +7873,22 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7894,7 +7937,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7909,30 +7952,30 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7946,7 +7989,7 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
@@ -7955,18 +7998,20 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8014,7 +8059,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8029,19 +8074,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8049,14 +8094,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8066,26 +8111,28 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8134,7 +8181,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8149,7 +8196,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
@@ -8158,10 +8205,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8183,7 +8230,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8195,15 +8242,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>160</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>161</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8252,19 +8301,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>163</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8279,7 +8328,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>164</v>
+        <v>460</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8287,14 +8336,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>136</v>
+        <v>462</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8310,21 +8359,21 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>137</v>
+        <v>463</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>138</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8372,7 +8421,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>170</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8384,7 +8433,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8396,10 +8445,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>164</v>
+        <v>454</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8407,46 +8456,42 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>161</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8494,19 +8539,19 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>163</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8521,7 +8566,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8529,21 +8574,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8555,20 +8600,18 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>463</v>
+        <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>464</v>
+        <v>166</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8616,19 +8659,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>462</v>
+        <v>170</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8643,7 +8686,7 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>467</v>
+        <v>164</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8651,42 +8694,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I55" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>469</v>
+        <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8734,22 +8781,22 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
@@ -8761,7 +8808,7 @@
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>473</v>
+        <v>134</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8769,14 +8816,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8786,7 +8833,7 @@
         <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -8803,9 +8850,11 @@
       <c r="M56" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="N56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8854,7 +8903,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8869,7 +8918,7 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
@@ -8878,10 +8927,10 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8889,10 +8938,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8900,22 +8949,22 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>182</v>
+        <v>482</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>483</v>
@@ -8948,13 +8997,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8972,13 +9021,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -8987,7 +9036,7 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
@@ -8996,10 +9045,10 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9007,24 +9056,24 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9033,19 +9082,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9094,13 +9141,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9109,7 +9156,7 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
@@ -9118,7 +9165,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>494</v>
@@ -9143,7 +9190,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9155,13 +9202,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>161</v>
+        <v>496</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>162</v>
+        <v>497</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9188,13 +9235,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9212,19 +9259,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>163</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9236,10 +9283,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>164</v>
+        <v>500</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9247,14 +9294,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9273,18 +9320,20 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>137</v>
+        <v>502</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>138</v>
+        <v>503</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>166</v>
+        <v>504</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9320,19 +9369,19 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>170</v>
+        <v>501</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9344,7 +9393,7 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9356,10 +9405,10 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>164</v>
+        <v>507</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9367,10 +9416,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9390,21 +9439,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>498</v>
+        <v>161</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>499</v>
+        <v>162</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>500</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9416,7 +9463,7 @@
         <v>82</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>82</v>
@@ -9428,13 +9475,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9452,7 +9499,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>504</v>
+        <v>163</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9464,7 +9511,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9476,10 +9523,10 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>506</v>
+        <v>164</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9487,21 +9534,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9510,21 +9557,21 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>508</v>
+        <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9536,7 +9583,7 @@
         <v>82</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>82</v>
@@ -9548,43 +9595,43 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>512</v>
+        <v>170</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9599,7 +9646,7 @@
         <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>513</v>
+        <v>164</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9607,10 +9654,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9624,28 +9671,26 @@
         <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>515</v>
+        <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9658,7 +9703,7 @@
         <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>82</v>
@@ -9670,13 +9715,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9694,7 +9739,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9709,7 +9754,7 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9763,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -9729,10 +9774,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9755,19 +9800,17 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>525</v>
+        <v>111</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9780,7 +9823,7 @@
         <v>82</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>82</v>
@@ -9792,13 +9835,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9816,7 +9859,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9840,10 +9883,10 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -9851,10 +9894,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9868,28 +9911,28 @@
         <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9938,7 +9981,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9953,7 +9996,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>82</v>
@@ -9962,10 +10005,10 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -9973,10 +10016,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9999,19 +10042,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10024,7 +10067,7 @@
         <v>82</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>82</v>
@@ -10060,7 +10103,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10084,10 +10127,10 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>82</v>
@@ -10095,10 +10138,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10121,15 +10164,17 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>160</v>
+        <v>548</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
         <v>552</v>
       </c>
@@ -10144,43 +10189,43 @@
         <v>82</v>
       </c>
       <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10207,7 +10252,7 @@
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
@@ -10215,10 +10260,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10241,15 +10286,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>385</v>
+        <v>528</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
         <v>559</v>
       </c>
@@ -10327,14 +10374,254 @@
         <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP68">
+  <autoFilter ref="A1:AP70">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10344,7 +10631,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,7 +630,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/63.52</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -639,7 +639,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1604-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1604-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/63.52</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,7 +630,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/63.52</t>
+    <t>http://va.gov/identifiers/$Sta3n/63.52</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -639,7 +639,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1604-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/63.52</t>
+    <t>1604-1: fixed value = http://va.gov/identifiers/$Sta3n/63.52</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
